--- a/artfynd/A 55280-2022 artfynd.xlsx
+++ b/artfynd/A 55280-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55280-2022 artfynd.xlsx
+++ b/artfynd/A 55280-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111224900</v>
       </c>
       <c r="B2" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591293.2432706917</v>
+        <v>591293</v>
       </c>
       <c r="R2" t="n">
-        <v>6831223.7747099</v>
+        <v>6831224</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111224901</v>
+        <v>111224902</v>
       </c>
       <c r="B3" t="n">
-        <v>78536</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591283.1098378194</v>
+        <v>591416</v>
       </c>
       <c r="R3" t="n">
-        <v>6831246.359872178</v>
+        <v>6831274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,21 +858,11 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -909,7 +879,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>låga av asp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -930,12 +900,7 @@
         <v>111224897</v>
       </c>
       <c r="B4" t="n">
-        <v>89665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,12 +917,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -971,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591418.1863659774</v>
+        <v>591418</v>
       </c>
       <c r="R4" t="n">
-        <v>6831223.27014201</v>
+        <v>6831223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,19 +969,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111224896</v>
+        <v>111224899</v>
       </c>
       <c r="B5" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1097,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591481.3967858786</v>
+        <v>591359</v>
       </c>
       <c r="R5" t="n">
-        <v>6831231.132917581</v>
+        <v>6831213</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,19 +1080,9 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,37 +1119,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111224898</v>
+        <v>111224901</v>
       </c>
       <c r="B6" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1223,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591399.6551599597</v>
+        <v>591283</v>
       </c>
       <c r="R6" t="n">
-        <v>6831202.783271533</v>
+        <v>6831246</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,21 +1191,11 @@
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-31</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1287,7 +1212,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1302,258 +1227,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>111224902</v>
-      </c>
-      <c r="B7" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>53</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Görsviken, Hls</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>591415.8861537643</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6831274.152232359</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Nianfors</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Lövrik och örtrik barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>låga av asp</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>111224899</v>
-      </c>
-      <c r="B8" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Görsviken, Hls</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>591359.3396854488</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6831212.667286294</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Nianfors</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2023-07-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Lövrik och örtrik barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
